--- a/List Fungsionalitas Website Crembo Media.xlsx
+++ b/List Fungsionalitas Website Crembo Media.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SURYA\UAJY\Semester 8\TA\Dokumen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e51c34aafd3930f/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A6BF99-0702-43C6-835A-71B4FE169BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{E12EA3F6-0785-4604-B8EB-DDD4ED72C8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15929953-C4AA-44B5-A52A-67EF8A00C54C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="912" xr2:uid="{B1B77A11-58E3-4FF1-8F41-DA80BA5C2135}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="268">
   <si>
     <t>No</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Pengguna harus login terlebih dahulu</t>
   </si>
   <si>
-    <t>Password lama harus valid</t>
-  </si>
-  <si>
     <t>Password baru harus memenuhi ketentuan keamanan</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>OTP masih berlaku</t>
   </si>
   <si>
-    <t>OTP valid dan belum kedaluwarsa</t>
-  </si>
-  <si>
     <t>Manajemen Tugas Streaming / Multimedia</t>
   </si>
   <si>
@@ -326,15 +320,6 @@
     <t>Pengambilan dan Pengembalian Barang</t>
   </si>
   <si>
-    <t>Permintaan disetujui admin</t>
-  </si>
-  <si>
-    <t>Sistem memperbarui status barang menjadi “tersedia” setelah barang dikembalikan</t>
-  </si>
-  <si>
-    <t>Pengembalian barang berhasil</t>
-  </si>
-  <si>
     <t>Pembatalan dan Riwayat Peminjaman</t>
   </si>
   <si>
@@ -362,21 +347,9 @@
     <t>Form Evaluasi Streaming / Misa</t>
   </si>
   <si>
-    <t>Sistem menyediakan halaman khusus form evaluasi pelayanan streaming misa yang dapat diakses tanpa login</t>
-  </si>
-  <si>
-    <t>Halaman evaluasi tersedia</t>
-  </si>
-  <si>
     <t>Menampilkan daftar jadwal misa yang belum memiliki data evaluasi</t>
   </si>
   <si>
-    <t>Sistem menyimpan hasil evaluasi dan mengirimkannya ke dashboard admin</t>
-  </si>
-  <si>
-    <t>Evaluasi belum pernah di isi</t>
-  </si>
-  <si>
     <t>Manajemen Informasi / Pengumuman</t>
   </si>
   <si>
@@ -410,9 +383,6 @@
     <t>Menghapus informasi/pengumuman</t>
   </si>
   <si>
-    <t>Manajemen Form Pendaftaran</t>
-  </si>
-  <si>
     <t>Membuat form pendaftaran kegiatan atau open recruitment baru</t>
   </si>
   <si>
@@ -503,12 +473,6 @@
     <t>Status anggota aktif (mewajibkan anggota menginput alasan pengajuan perubahan status menjadi nonaktif)</t>
   </si>
   <si>
-    <t>Sistem menyimpan permintaan perubahan status anggota menjadi nonaktif</t>
-  </si>
-  <si>
-    <t>Data permintaan valid</t>
-  </si>
-  <si>
     <t>Melihat daftar permintaan perubahan status anggota</t>
   </si>
   <si>
@@ -518,18 +482,6 @@
     <t>Menyetujui atau menolak permintaan perubahan status anggota menjadi nonaktif/aktif</t>
   </si>
   <si>
-    <t xml:space="preserve">Sistem mengubah status anggota </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menjadi nonaktif jika permintaan disetujui oleh admin/mempertahankan status anggota tetap aktif jika permintaan perubahan status ditolak </t>
-  </si>
-  <si>
-    <t>Sistem membatasi anggota dengan status nonaktif</t>
-  </si>
-  <si>
-    <t>Tidak dapat melakukan regostrasi tugas streamoing, peminjaman barang, pendaftaran kegiatan internal.</t>
-  </si>
-  <si>
     <t>Membuat jadwal misa besar</t>
   </si>
   <si>
@@ -704,18 +656,6 @@
     <t>Pengajuan status dibuat</t>
   </si>
   <si>
-    <t>Memasukkan password lama sebelum mengganti password baru</t>
-  </si>
-  <si>
-    <t>Memasukkan password baru dan konfirmasi password baru</t>
-  </si>
-  <si>
-    <t>Memasukkan identitas (email,/no wa/username) yang terdaftar untuk proses reset password</t>
-  </si>
-  <si>
-    <t>Membuat password baru setelah OTP berhasil diverifikasi</t>
-  </si>
-  <si>
     <t>Menampilkan halaman lupa password</t>
   </si>
   <si>
@@ -776,9 +716,6 @@
     <t>Menampilkan total jumlah tugas yang harus dipenuhi oleh setiap anggota pada bulan berikutnya berdasarkan kekurangan bulan sebelumnya</t>
   </si>
   <si>
-    <t>Memilih tanggal dan waktu misa yang akan diisi evaluasinya</t>
-  </si>
-  <si>
     <t>Menampilkan informasi dasar misa seperti tanggal, waktu, dan petugas yang bertugas</t>
   </si>
   <si>
@@ -791,30 +728,15 @@
     <t xml:space="preserve">Menambahkan data inventaris barang baru </t>
   </si>
   <si>
-    <t>Hak akses admin, data barang harus lengkap, input informasi barang seperti nomor barang, nama barang, kode barang, tanggal pembelian, jumlah stok, kondisi barang (baik, rusak, hilang), status barang (bisa dipinjam, atau tidak)</t>
-  </si>
-  <si>
     <t>Memperbarui status barang menjadi “dipinjam” setelah permintaan disetujui</t>
   </si>
   <si>
     <t>Mengajukan permohonan peminjaman barang (input tanggal peminjaman, keperluan dan tanggal pengembalian barang)</t>
   </si>
   <si>
-    <t>Mengunggah foto bukti pengambilan barang setelah peminjaman disetujui serta menginput jam pengambilan dan tanggal serta lokasi saat barang di ambil</t>
-  </si>
-  <si>
-    <t>Mengunggah foto bukti pengembalian barang serta menginput jam pengembalian dan tanggal pengembalian serta lokasi posisi barang saat dikembalikan</t>
-  </si>
-  <si>
     <t>Manajemen laporan</t>
   </si>
   <si>
-    <t xml:space="preserve">Memilih jenis laporan yang akan diunduh </t>
-  </si>
-  <si>
-    <t>Pilihan laporan tersedia (jadwal, anggota, inventaris, dll)</t>
-  </si>
-  <si>
     <t>Mengunduh laporan jadwal tugas streaming</t>
   </si>
   <si>
@@ -830,32 +752,101 @@
     <t>Mengunduh laporan peminjaman barang</t>
   </si>
   <si>
-    <t>Data evaluasi tersedia</t>
-  </si>
-  <si>
     <t>Mengunduh laporan evaluasi misa/streaming</t>
   </si>
   <si>
     <t>Mengunduh laporan aktivitas/log sistem</t>
   </si>
   <si>
-    <t>Hak akses super admin</t>
-  </si>
-  <si>
     <t>Memfilter data laporan berdasarkan rentang tanggal</t>
   </si>
   <si>
-    <t>Mengunduh laporan data dalam format PDF atau Excel</t>
-  </si>
-  <si>
-    <t>Format file di dukung</t>
+    <t>Verifikasi identitas (email,/no wa/username) yang terdaftar untuk proses reset password</t>
+  </si>
+  <si>
+    <t>Verifikasi  password baru dan konfirmasi password baru</t>
+  </si>
+  <si>
+    <t>Hak akses admin, Menjadi nonaktif jika permintaan disetujui oleh admin/mempertahankan status anggota tetap aktif jika permintaan perubahan status ditolak, Tidak dapat melakukan regostrasi tugas streamoing, peminjaman barang, pendaftaran kegiatan internal.</t>
+  </si>
+  <si>
+    <t>Hak akses admin, sesuaikan konstrain</t>
+  </si>
+  <si>
+    <t>Mencari data anggota</t>
+  </si>
+  <si>
+    <t>Search by nama, role dll</t>
+  </si>
+  <si>
+    <t>Mencari daftar agenda kegiatan</t>
+  </si>
+  <si>
+    <t>Search by judul, kategori, tanggal dll</t>
+  </si>
+  <si>
+    <t>Manajemen Form Pendaftaran (dipisah antara oprec dan kegiatan umum)</t>
+  </si>
+  <si>
+    <t>Konstrain tambahakan melalui email atau wa atau hanya di website saja untuk ntif</t>
+  </si>
+  <si>
+    <t>Data jadwal tersedia, Sistem menyediakan halaman khusus form evaluasi pelayanan streaming misa yang dapat diakses tanpa login, Memilih tanggal dan waktu misa yang akan diisi evaluasinya</t>
+  </si>
+  <si>
+    <t>Mengisi detail hasil evaluasi streaming</t>
+  </si>
+  <si>
+    <t>Mencari data inventaris barang</t>
+  </si>
+  <si>
+    <t>Search by nama, kode, kategori dll.</t>
+  </si>
+  <si>
+    <t>Permintaan disetujui admin, Mengunggah foto bukti pengambilan barang setelah peminjaman disetujui serta menginput jam pengambilan dan tanggal serta lokasi saat barang di ambil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengunggah foto bukti pengambilan barang </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengunggah foto bukti pengembalian barang </t>
+  </si>
+  <si>
+    <t>Mengunggah foto bukti pengembalian barang serta menginput jam pengembalian dan tanggal pengembalian serta lokasi posisi barang saat dikembalikan, Sistem memperbarui status barang menjadi “tersedia” setelah barang dikembalikan</t>
+  </si>
+  <si>
+    <t>Data jadwal tersedia, menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Data monitoring tersedia,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Data anggota tersedia,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Data inventaris tersedia,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Data peminjaman tersedia,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Data evaluasi tersedia,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Hak akses super admin,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Format file di dukung,  menampilkan dan memfilter</t>
+  </si>
+  <si>
+    <t>Hak akses admin, data barang harus lengkap, input informasi barang seperti nomor barang, nama barang, kode barang, tanggal pembelian, jumlah stok, kondisi barang (baik, rusak, hilang), status barang (bisa dipinjam, atau tidak), foto barang.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -897,17 +888,12 @@
       <name val="Poppins"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Poppins"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -936,6 +922,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1040,7 +1032,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1123,7 +1115,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1135,7 +1127,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1186,9 +1178,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1198,15 +1187,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1300,6 +1295,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1624,42 +1623,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C116429-95FB-4524-9744-FE8A6E7119EE}">
-  <dimension ref="A2:D172"/>
+  <dimension ref="A2:F163"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="3.77734375" style="6" customWidth="1"/>
     <col min="2" max="2" width="57.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="31.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46.5546875" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="29.77734375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="61" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="60"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="61"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A4" s="35"/>
       <c r="B4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="56"/>
+      <c r="C4" s="55"/>
       <c r="D4" s="36"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.6">
@@ -1691,7 +1691,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>5</v>
@@ -1727,7 +1727,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>5</v>
@@ -1738,7 +1738,7 @@
       <c r="A11" s="12">
         <v>7</v>
       </c>
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="54" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="12" t="s">
@@ -1750,7 +1750,7 @@
       <c r="A12" s="12">
         <v>8</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="B12" s="54" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -1763,7 +1763,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>5</v>
@@ -1772,7 +1772,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A14" s="32"/>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="56" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="32"/>
@@ -1814,7 +1814,7 @@
       <c r="C17" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="53" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1831,13 +1831,13 @@
         <v>12</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
@@ -1845,13 +1845,13 @@
         <v>13</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C20" s="22" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
@@ -1859,1944 +1859,1831 @@
         <v>14</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A22" s="22">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="104.4" x14ac:dyDescent="0.6">
       <c r="A23" s="22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A24" s="22">
-        <v>17</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>159</v>
+        <v>20</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>209</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
-      <c r="A25" s="22">
-        <v>18</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A26" s="22">
-        <v>19</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.6">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="41"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="41"/>
+    </row>
+    <row r="27" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
       <c r="A27" s="22">
-        <v>20</v>
-      </c>
-      <c r="B27" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>42</v>
+        <v>21</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>40</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A28" s="25"/>
-      <c r="B28" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="41"/>
+      <c r="A28" s="22">
+        <v>22</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A29" s="25"/>
-      <c r="B29" s="26" t="s">
+      <c r="A29" s="22">
+        <v>23</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A30" s="22">
+        <v>24</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="41"/>
-    </row>
-    <row r="30" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
-      <c r="A30" s="22">
-        <v>21</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>143</v>
-      </c>
       <c r="C30" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>147</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A31" s="22">
+      <c r="A31" s="22"/>
+      <c r="B31" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A32" s="25"/>
+      <c r="B32" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A32" s="22">
-        <v>23</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>41</v>
-      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="27"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A33" s="22">
+        <v>25</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="27"/>
+      <c r="A34" s="22">
+        <v>27</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A35" s="22">
-        <v>25</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>24</v>
+      <c r="D35" s="53" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A36" s="22">
-        <v>26</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>222</v>
+        <v>29</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>241</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D36" s="54" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="D36" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
       <c r="A37" s="22">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="54" t="s">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A38" s="22">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="54" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A39" s="22">
-        <v>29</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
+        <v>8</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A39" s="25"/>
+      <c r="B39" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="27"/>
+    </row>
+    <row r="40" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
       <c r="A40" s="22">
-        <v>30</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>105</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A41" s="22">
-        <v>31</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>107</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="54" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A42" s="22">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A43" s="25"/>
-      <c r="B43" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A43" s="22">
+        <v>36</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="27"/>
-    </row>
-    <row r="44" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A44" s="22">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B44" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A45" s="22">
+        <v>38</v>
+      </c>
+      <c r="B45" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C44" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D44" s="54" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A45" s="22">
-        <v>34</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D45" s="54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A46" s="22">
-        <v>35</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C46" s="21" t="s">
+      <c r="C45" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A46" s="25"/>
+      <c r="B46" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" s="25"/>
+      <c r="D46" s="27"/>
+    </row>
+    <row r="47" spans="1:4" ht="104.4" x14ac:dyDescent="0.6">
+      <c r="A47" s="22">
+        <v>39</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A48" s="22">
+        <v>40</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C48" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D46" s="54" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A47" s="22">
-        <v>36</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A48" s="22">
-        <v>37</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="54" t="s">
-        <v>118</v>
+      <c r="D48" s="53" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A49" s="22">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A50" s="22">
         <v>42</v>
       </c>
-      <c r="D49" s="54" t="s">
+      <c r="B50" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A51" s="22">
+        <v>43</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A52" s="22"/>
+      <c r="B52" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A53" s="25"/>
+      <c r="B53" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="27"/>
+    </row>
+    <row r="54" spans="1:4" ht="132" x14ac:dyDescent="0.6">
+      <c r="A54" s="22">
+        <v>44</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A55" s="22">
+        <v>45</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A56" s="22">
+        <v>46</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="53" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A50" s="25"/>
-      <c r="B50" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="27"/>
-    </row>
-    <row r="51" spans="1:4" ht="104.4" x14ac:dyDescent="0.6">
-      <c r="A51" s="22">
-        <v>39</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C51" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A52" s="22">
-        <v>40</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="C52" s="52" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="54" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A53" s="22">
-        <v>41</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C53" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" s="54" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A54" s="22">
-        <v>42</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="C54" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A55" s="22">
-        <v>43</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C55" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="D55" s="54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A56" s="25"/>
-      <c r="B56" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C56" s="25"/>
-      <c r="D56" s="27"/>
-    </row>
-    <row r="57" spans="1:4" ht="132" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A57" s="22">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D57" s="54" t="s">
-        <v>126</v>
+        <v>17</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A58" s="22">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="54" t="s">
-        <v>127</v>
+        <v>8</v>
+      </c>
+      <c r="D58" s="53" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A59" s="22">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>232</v>
+        <v>121</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A60" s="22">
+        <v>50</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="53" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
+      <c r="A61" s="22">
+        <v>51</v>
+      </c>
+      <c r="B61" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D61" s="53" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A62" s="22">
+        <v>52</v>
+      </c>
+      <c r="B62" s="18" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A60" s="22">
-        <v>47</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="54" t="s">
+      <c r="C62" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D62" s="53" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A61" s="22">
-        <v>48</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="54" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A62" s="22">
-        <v>49</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="54" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A63" s="22">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C63" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D63" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A64" s="22">
+        <v>54</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D64" s="53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A65" s="25"/>
+      <c r="B65" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" s="25"/>
+      <c r="D65" s="27"/>
+    </row>
+    <row r="66" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A66" s="22">
+        <v>55</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="54" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
-      <c r="A64" s="22">
-        <v>51</v>
-      </c>
-      <c r="B64" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="54" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A65" s="22">
-        <v>52</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C65" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D65" s="54" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A66" s="22">
-        <v>53</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D66" s="54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="D66" s="53" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A67" s="22">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D67" s="54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A68" s="25"/>
-      <c r="B68" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67" s="53" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A68" s="22">
+        <v>57</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="26.4" x14ac:dyDescent="0.6">
+      <c r="A69" s="22">
+        <v>58</v>
+      </c>
+      <c r="B69" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69" s="53" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A70" s="22">
+        <v>59</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A71" s="22">
+        <v>60</v>
+      </c>
+      <c r="B71" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A72" s="22">
+        <v>61</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="53" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A73" s="22">
+        <v>62</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="53" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A74" s="22">
+        <v>63</v>
+      </c>
+      <c r="B74" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C68" s="25"/>
-      <c r="D68" s="27"/>
-    </row>
-    <row r="69" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A69" s="22">
-        <v>55</v>
-      </c>
-      <c r="B69" s="18" t="s">
+      <c r="C74" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="53" t="s">
         <v>169</v>
       </c>
-      <c r="C69" s="21" t="s">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A75" s="25"/>
+      <c r="B75" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C75" s="25"/>
+      <c r="D75" s="27"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A76" s="22">
+        <v>66</v>
+      </c>
+      <c r="B76" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D76" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="F76" s="59"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A77" s="22">
+        <v>67</v>
+      </c>
+      <c r="B77" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="F77" s="59"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A78" s="22">
+        <v>68</v>
+      </c>
+      <c r="B78" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D78" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="F78" s="59"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A79" s="22">
+        <v>69</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="F79" s="59"/>
+    </row>
+    <row r="80" spans="1:6" ht="26.4" x14ac:dyDescent="0.6">
+      <c r="A80" s="22">
+        <v>70</v>
+      </c>
+      <c r="B80" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D80" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="F80" s="59"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A81" s="22">
+        <v>71</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D81" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="F81" s="59"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A82" s="22">
+        <v>72</v>
+      </c>
+      <c r="B82" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="D82" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="F82" s="59"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A83" s="22">
+        <v>73</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="F83" s="59"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A84" s="25"/>
+      <c r="B84" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="25"/>
+      <c r="D84" s="27"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A85" s="25"/>
+      <c r="B85" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="C85" s="25"/>
+      <c r="D85" s="27"/>
+    </row>
+    <row r="86" spans="1:6" ht="52.2" x14ac:dyDescent="0.6">
+      <c r="A86" s="22">
+        <v>74</v>
+      </c>
+      <c r="B86" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="C86" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D69" s="54" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A70" s="22">
-        <v>56</v>
-      </c>
-      <c r="B70" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C70" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D70" s="54" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A71" s="22">
-        <v>57</v>
-      </c>
-      <c r="B71" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C71" s="21" t="s">
+      <c r="D86" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="E86" s="58" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A87" s="22">
+        <v>75</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D71" s="54" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
-      <c r="A72" s="22">
-        <v>58</v>
-      </c>
-      <c r="B72" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D72" s="54" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A73" s="22">
-        <v>59</v>
-      </c>
-      <c r="B73" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C73" s="21" t="s">
+      <c r="D87" s="53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A88" s="22">
+        <v>76</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C88" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A74" s="22">
-        <v>60</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D74" s="54" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A75" s="22">
-        <v>61</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C75" s="21" t="s">
+      <c r="D88" s="53" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A89" s="22">
+        <v>77</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C89" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D75" s="54" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A76" s="22">
-        <v>62</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" s="54" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A77" s="22">
-        <v>63</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D77" s="54" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A78" s="25"/>
-      <c r="B78" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C78" s="25"/>
-      <c r="D78" s="27"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A79" s="22">
-        <v>64</v>
-      </c>
-      <c r="B79" s="54" t="s">
-        <v>269</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D79" s="54" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
-      <c r="A80" s="22">
-        <v>65</v>
-      </c>
-      <c r="B80" s="54" t="s">
-        <v>257</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D80" s="54" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A81" s="22">
-        <v>66</v>
-      </c>
-      <c r="B81" s="54" t="s">
-        <v>259</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D81" s="54" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A82" s="22">
-        <v>67</v>
-      </c>
-      <c r="B82" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D82" s="54" t="s">
+      <c r="D89" s="53" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="39.6" x14ac:dyDescent="0.6">
+      <c r="A90" s="22">
+        <v>78</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="53" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A91" s="25"/>
+      <c r="B91" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="C91" s="25"/>
+      <c r="D91" s="27"/>
+    </row>
+    <row r="92" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A92" s="22">
         <v>79</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A83" s="22">
-        <v>68</v>
-      </c>
-      <c r="B83" s="54" t="s">
-        <v>261</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D83" s="54" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A84" s="22">
-        <v>69</v>
-      </c>
-      <c r="B84" s="54" t="s">
-        <v>262</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A85" s="22">
-        <v>70</v>
-      </c>
-      <c r="B85" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D85" s="54" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A86" s="22">
-        <v>71</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D86" s="54" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A87" s="22">
-        <v>72</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D87" s="54" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A88" s="22">
-        <v>73</v>
-      </c>
-      <c r="B88" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C88" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D88" s="54" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A89" s="25"/>
-      <c r="B89" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C89" s="25"/>
-      <c r="D89" s="27"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A90" s="25"/>
-      <c r="B90" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C90" s="25"/>
-      <c r="D90" s="27"/>
-    </row>
-    <row r="91" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
-      <c r="A91" s="22">
-        <v>74</v>
-      </c>
-      <c r="B91" s="53" t="s">
-        <v>196</v>
-      </c>
-      <c r="C91" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="54" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A92" s="22">
-        <v>75</v>
-      </c>
       <c r="B92" s="24" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C92" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D92" s="54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="D92" s="53" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A93" s="22">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B93" s="24" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C93" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D93" s="54" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="D93" s="53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A94" s="22">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C94" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="54" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
-      <c r="A95" s="22">
-        <v>78</v>
-      </c>
-      <c r="B95" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="C95" s="21" t="s">
+      <c r="D94" s="53" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="A95" s="25"/>
+      <c r="B95" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="C95" s="25"/>
+      <c r="D95" s="27"/>
+    </row>
+    <row r="96" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A96" s="22">
+        <v>82</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D95" s="54" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A96" s="25"/>
-      <c r="B96" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="C96" s="25"/>
-      <c r="D96" s="27"/>
-    </row>
-    <row r="97" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="D96" s="53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
       <c r="A97" s="22">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B97" s="24" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C97" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D97" s="54" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A98" s="22">
-        <v>80</v>
-      </c>
-      <c r="B98" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="54" t="s">
-        <v>210</v>
-      </c>
+      <c r="D97" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A98" s="25"/>
+      <c r="B98" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" s="25"/>
+      <c r="D98" s="27"/>
     </row>
     <row r="99" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A99" s="22">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B99" s="24" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C99" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D99" s="54" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A100" s="25"/>
-      <c r="B100" s="26" t="s">
+      <c r="D99" s="53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A100" s="22">
+        <v>85</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A101" s="25"/>
+      <c r="B101" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C101" s="25"/>
+      <c r="D101" s="27"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A102" s="25"/>
+      <c r="B102" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C102" s="25"/>
+      <c r="D102" s="27"/>
+    </row>
+    <row r="103" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A103" s="22">
+        <v>86</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
+      <c r="A104" s="22">
+        <v>87</v>
+      </c>
+      <c r="B104" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="25"/>
-      <c r="D100" s="27"/>
-    </row>
-    <row r="101" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A101" s="22">
-        <v>82</v>
-      </c>
-      <c r="B101" s="24" t="s">
+      <c r="C104" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="30" t="s">
         <v>214</v>
-      </c>
-      <c r="C101" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D101" s="54" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
-      <c r="A102" s="22">
-        <v>83</v>
-      </c>
-      <c r="B102" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="C102" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D102" s="54" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A103" s="25"/>
-      <c r="B103" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="C103" s="25"/>
-      <c r="D103" s="27"/>
-    </row>
-    <row r="104" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A104" s="22">
-        <v>84</v>
-      </c>
-      <c r="B104" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="C104" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="54" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A105" s="22">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B105" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="54" t="s">
-        <v>210</v>
+        <v>37</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="30" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A106" s="25"/>
       <c r="B106" s="26" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C106" s="25"/>
-      <c r="D106" s="27"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A107" s="25"/>
-      <c r="B107" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C107" s="25"/>
-      <c r="D107" s="27"/>
+      <c r="D106" s="41"/>
+    </row>
+    <row r="107" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A107" s="22">
+        <v>89</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D107" s="16" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="108" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A108" s="22">
-        <v>86</v>
-      </c>
-      <c r="B108" s="18" t="s">
-        <v>36</v>
+        <v>90</v>
+      </c>
+      <c r="B108" s="23" t="s">
+        <v>150</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D108" s="54" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A109" s="22">
-        <v>87</v>
-      </c>
-      <c r="B109" s="23" t="s">
-        <v>233</v>
+        <v>91</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>215</v>
       </c>
       <c r="C109" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A110" s="22">
-        <v>88</v>
-      </c>
-      <c r="B110" s="24" t="s">
-        <v>39</v>
+        <v>92</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>151</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>62</v>
+        <v>217</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A111" s="25"/>
       <c r="B111" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C111" s="25"/>
       <c r="D111" s="41"/>
     </row>
-    <row r="112" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="A112" s="22">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B112" s="18" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D112" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="A113" s="22">
-        <v>90</v>
-      </c>
-      <c r="B113" s="23" t="s">
-        <v>166</v>
+        <v>94</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>44</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D113" s="16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>8</v>
+      </c>
+      <c r="D113" s="53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="A114" s="22">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B114" s="18" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="C114" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A115" s="25"/>
+      <c r="B115" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C115" s="25"/>
+      <c r="D115" s="41"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A116" s="16">
+        <v>96</v>
+      </c>
+      <c r="B116" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C116" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D114" s="30" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A115" s="22">
-        <v>92</v>
-      </c>
-      <c r="B115" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="C115" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D115" s="30" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A116" s="25"/>
-      <c r="B116" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C116" s="25"/>
-      <c r="D116" s="41"/>
-    </row>
-    <row r="117" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A117" s="22">
-        <v>93</v>
-      </c>
-      <c r="B117" s="18" t="s">
-        <v>45</v>
+      <c r="D116" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A117" s="16">
+        <v>97</v>
+      </c>
+      <c r="B117" s="33" t="s">
+        <v>219</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D117" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A118" s="22">
-        <v>94</v>
-      </c>
-      <c r="B118" s="18" t="s">
-        <v>46</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A118" s="16">
+        <v>98</v>
+      </c>
+      <c r="B118" s="29" t="s">
+        <v>51</v>
       </c>
       <c r="C118" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D118" s="54" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A119" s="22">
-        <v>95</v>
-      </c>
-      <c r="B119" s="18" t="s">
-        <v>49</v>
+      <c r="D118" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A119" s="16">
+        <v>99</v>
+      </c>
+      <c r="B119" s="29" t="s">
+        <v>53</v>
       </c>
       <c r="C119" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D119" s="54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A120" s="25"/>
-      <c r="B120" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C120" s="25"/>
-      <c r="D120" s="41"/>
+      <c r="D119" s="30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
+      <c r="A120" s="16">
+        <v>100</v>
+      </c>
+      <c r="B120" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="16" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A121" s="16">
-        <v>96</v>
-      </c>
-      <c r="B121" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D121" s="16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A122" s="16">
-        <v>97</v>
-      </c>
-      <c r="B122" s="33" t="s">
-        <v>239</v>
+      <c r="A121" s="25"/>
+      <c r="B121" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C121" s="27"/>
+      <c r="D121" s="41"/>
+    </row>
+    <row r="122" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="22">
+        <v>101</v>
+      </c>
+      <c r="B122" s="18" t="s">
+        <v>58</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D122" s="16" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A123" s="16">
-        <v>98</v>
-      </c>
-      <c r="B123" s="29" t="s">
-        <v>53</v>
+        <v>40</v>
+      </c>
+      <c r="D122" s="29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A123" s="22">
+        <v>102</v>
+      </c>
+      <c r="B123" s="18" t="s">
+        <v>59</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A124" s="16">
-        <v>99</v>
-      </c>
-      <c r="B124" s="29" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="D123" s="33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A124" s="22">
+        <v>103</v>
+      </c>
+      <c r="B124" s="18" t="s">
+        <v>61</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
-      <c r="A125" s="16">
-        <v>100</v>
-      </c>
-      <c r="B125" s="30" t="s">
-        <v>57</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A125" s="22">
+        <v>104</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="C125" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A126" s="25"/>
-      <c r="B126" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="C126" s="27"/>
+      <c r="D125" s="30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A126" s="43"/>
+      <c r="B126" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C126" s="28"/>
       <c r="D126" s="41"/>
     </row>
-    <row r="127" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A127" s="22">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D127" s="29" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A128" s="22">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B128" s="18" t="s">
-        <v>61</v>
+        <v>221</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D128" s="33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+      <c r="D128" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A129" s="22">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>63</v>
+        <v>222</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D129" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="D129" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A130" s="22">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B130" s="18" t="s">
-        <v>64</v>
+        <v>223</v>
       </c>
       <c r="C130" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D130" s="29"/>
+    </row>
+    <row r="131" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A131" s="22">
+        <v>109</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C131" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D130" s="30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.6">
-      <c r="A131" s="43"/>
-      <c r="B131" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C131" s="28"/>
-      <c r="D131" s="41"/>
+      <c r="D131" s="29" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="132" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A132" s="22">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B132" s="18" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D132" s="29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+      <c r="D132" s="30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
       <c r="A133" s="22">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D133" s="29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A134" s="22">
-        <v>107</v>
-      </c>
-      <c r="B134" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="C134" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D134" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D133" s="30" t="s">
         <v>70</v>
       </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A134" s="43"/>
+      <c r="B134" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C134" s="28"/>
+      <c r="D134" s="41"/>
     </row>
     <row r="135" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A135" s="22">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>243</v>
+        <v>72</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D135" s="29"/>
+        <v>76</v>
+      </c>
+      <c r="D135" s="29" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="136" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A136" s="22">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B136" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C136" s="21" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="D136" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A137" s="22">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D137" s="30" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
+        <v>76</v>
+      </c>
+      <c r="D137" s="29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A138" s="22">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B138" s="18" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D138" s="30" t="s">
-        <v>72</v>
+        <v>76</v>
+      </c>
+      <c r="D138" s="29" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A139" s="43"/>
-      <c r="B139" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C139" s="28"/>
-      <c r="D139" s="41"/>
-    </row>
-    <row r="140" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A139" s="47"/>
+      <c r="B139" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C139" s="49"/>
+      <c r="D139" s="50"/>
+    </row>
+    <row r="140" spans="1:4" ht="52.8" x14ac:dyDescent="0.6">
       <c r="A140" s="22">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B140" s="18" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D140" s="29" t="s">
-        <v>79</v>
+        <v>5</v>
+      </c>
+      <c r="D140" s="53" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A141" s="22">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>75</v>
+        <v>226</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D141" s="29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>5</v>
+      </c>
+      <c r="D141" s="53"/>
+    </row>
+    <row r="142" spans="1:4" ht="39.6" x14ac:dyDescent="0.6">
       <c r="A142" s="22">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B142" s="18" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D142" s="29" t="s">
-        <v>79</v>
+        <v>5</v>
+      </c>
+      <c r="D142" s="53" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A143" s="22">
-        <v>112</v>
-      </c>
-      <c r="B143" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C143" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B143" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D143" s="16"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A144" s="43"/>
+      <c r="B144" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="D143" s="29" t="s">
+      <c r="C144" s="28"/>
+      <c r="D144" s="41"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A145" s="43"/>
+      <c r="B145" s="40" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A144" s="47"/>
-      <c r="B144" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="C144" s="49"/>
-      <c r="D144" s="50"/>
-    </row>
-    <row r="145" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A145" s="22">
-        <v>113</v>
-      </c>
-      <c r="B145" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="C145" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D145" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="C145" s="28"/>
+      <c r="D145" s="41"/>
+    </row>
+    <row r="146" spans="1:4" ht="87" x14ac:dyDescent="0.6">
       <c r="A146" s="22">
-        <v>114</v>
-      </c>
-      <c r="B146" s="18" t="s">
-        <v>110</v>
+        <v>121</v>
+      </c>
+      <c r="B146" s="24" t="s">
+        <v>229</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D146" s="54" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="D146" s="44" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A147" s="22">
-        <v>115</v>
-      </c>
-      <c r="B147" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C147" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D147" s="54" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>122</v>
+      </c>
+      <c r="B147" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C147" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" s="44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A148" s="22">
-        <v>116</v>
-      </c>
-      <c r="B148" s="18" t="s">
-        <v>247</v>
+        <v>123</v>
+      </c>
+      <c r="B148" s="45" t="s">
+        <v>83</v>
       </c>
       <c r="C148" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D148" s="54"/>
-    </row>
-    <row r="149" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
+        <v>40</v>
+      </c>
+      <c r="D148" s="30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A149" s="22">
-        <v>117</v>
-      </c>
-      <c r="B149" s="18" t="s">
-        <v>248</v>
+        <v>124</v>
+      </c>
+      <c r="B149" s="45" t="s">
+        <v>84</v>
       </c>
       <c r="C149" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D149" s="54"/>
-    </row>
-    <row r="150" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A150" s="22">
-        <v>118</v>
-      </c>
-      <c r="B150" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C150" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D149" s="30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A150" s="22"/>
+      <c r="B150" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="C150" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D150" s="30" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A151" s="43"/>
+      <c r="B151" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C151" s="43"/>
+      <c r="D151" s="42"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A152" s="22">
+        <v>125</v>
+      </c>
+      <c r="B152" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C152" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D152" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A153" s="22">
+        <v>126</v>
+      </c>
+      <c r="B153" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="C153" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D153" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+      <c r="A154" s="22">
+        <v>127</v>
+      </c>
+      <c r="B154" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C154" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D150" s="16"/>
-    </row>
-    <row r="151" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A151" s="22">
-        <v>119</v>
-      </c>
-      <c r="B151" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C151" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="16"/>
-    </row>
-    <row r="152" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A152" s="22">
-        <v>120</v>
-      </c>
-      <c r="B152" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C152" s="22" t="s">
+      <c r="D154" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
+      <c r="A155" s="22">
+        <v>128</v>
+      </c>
+      <c r="B155" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C155" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D155" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A156" s="43"/>
+      <c r="B156" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="D152" s="16"/>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A153" s="43"/>
-      <c r="B153" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C153" s="28"/>
-      <c r="D153" s="41"/>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A154" s="43"/>
-      <c r="B154" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C154" s="28"/>
-      <c r="D154" s="41"/>
-    </row>
-    <row r="155" spans="1:4" ht="87" x14ac:dyDescent="0.6">
-      <c r="A155" s="22">
-        <v>121</v>
-      </c>
-      <c r="B155" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="C155" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D155" s="44" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A156" s="22">
-        <v>122</v>
-      </c>
-      <c r="B156" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C156" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="C156" s="46"/>
+      <c r="D156" s="42"/>
+    </row>
+    <row r="157" spans="1:4" ht="69.599999999999994" x14ac:dyDescent="0.6">
       <c r="A157" s="22">
-        <v>123</v>
-      </c>
-      <c r="B157" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C157" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D157" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.6">
+        <v>129</v>
+      </c>
+      <c r="B157" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D157" s="16" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="87" x14ac:dyDescent="0.6">
       <c r="A158" s="22">
-        <v>124</v>
-      </c>
-      <c r="B158" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C158" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D158" s="30" t="s">
-        <v>41</v>
+        <v>130</v>
+      </c>
+      <c r="B158" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="C158" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D158" s="16" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A159" s="43"/>
+      <c r="A159" s="25"/>
       <c r="B159" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C159" s="43"/>
-      <c r="D159" s="42"/>
+        <v>94</v>
+      </c>
+      <c r="C159" s="27"/>
+      <c r="D159" s="41"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.6">
       <c r="A160" s="22">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B160" s="24" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C160" s="22" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D160" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
       <c r="A161" s="22">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B161" s="24" t="s">
-        <v>253</v>
+        <v>96</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D161" s="16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
       <c r="A162" s="22">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B162" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C162" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D162" s="30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" ht="26.4" x14ac:dyDescent="0.6">
-      <c r="A163" s="22">
-        <v>128</v>
-      </c>
-      <c r="B163" s="34" t="s">
-        <v>252</v>
-      </c>
-      <c r="C163" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D163" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A164" s="43"/>
-      <c r="B164" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C164" s="46"/>
-      <c r="D164" s="42"/>
-    </row>
-    <row r="165" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
-      <c r="A165" s="22">
-        <v>129</v>
-      </c>
-      <c r="B165" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="C165" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D165" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" ht="52.2" x14ac:dyDescent="0.6">
-      <c r="A166" s="22">
-        <v>130</v>
-      </c>
-      <c r="B166" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="C166" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D166" s="16"/>
-    </row>
-    <row r="167" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A167" s="22">
-        <v>131</v>
-      </c>
-      <c r="B167" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="C167" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D167" s="16" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A168" s="25"/>
-      <c r="B168" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="C168" s="27"/>
-      <c r="D168" s="41"/>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A169" s="22">
-        <v>132</v>
-      </c>
-      <c r="B169" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C169" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D169" s="16" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" s="5" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A170" s="22">
-        <v>133</v>
-      </c>
-      <c r="B170" s="24" t="s">
+      <c r="C162" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D162" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C170" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D170" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" ht="34.799999999999997" x14ac:dyDescent="0.6">
-      <c r="A171" s="22">
-        <v>134</v>
-      </c>
-      <c r="B171" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="C171" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D171" s="16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.6">
-      <c r="A172" s="32"/>
-      <c r="B172" s="37"/>
-      <c r="C172" s="38"/>
-      <c r="D172" s="39"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.6">
+      <c r="A163" s="32"/>
+      <c r="B163" s="37"/>
+      <c r="C163" s="38"/>
+      <c r="D163" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/List Fungsionalitas Website Crembo Media.xlsx
+++ b/List Fungsionalitas Website Crembo Media.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e51c34aafd3930f/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SURYA\UAJY\Semester 8\TA\Wireframe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{E12EA3F6-0785-4604-B8EB-DDD4ED72C8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15929953-C4AA-44B5-A52A-67EF8A00C54C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49FD142-BCC4-4CE2-9E02-DBAC47031907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="912" xr2:uid="{B1B77A11-58E3-4FF1-8F41-DA80BA5C2135}"/>
   </bookViews>
@@ -1295,10 +1295,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2670,7 +2666,7 @@
         <v>239</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
       <c r="D82" s="53" t="s">
         <v>265</v>
